--- a/jpcore-r4/feature/medication_example_line_cs/StructureDefinition-jp-medicationdosage-ratecomment.xlsx
+++ b/jpcore-r4/feature/medication_example_line_cs/StructureDefinition-jp-medicationdosage-ratecomment.xlsx
@@ -132,7 +132,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:Dosage</t>
+    <t>element:Dosage.doseAndRate</t>
   </si>
   <si>
     <t>element:MedicationAdministration.dosage.doseAndRate</t>
